--- a/data/testData.xlsx
+++ b/data/testData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wdtablesystems-my.sharepoint.com/personal/prasad_kamble_wdtablesystems_com/Documents/Documents/PlayWrightProject/PlayWright_POC/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wdtablesystems-my.sharepoint.com/personal/arun_kumar_wdtablesystems_com/Documents/Desktop/PlayWright/Project_TableUI/TableUI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="220" documentId="11_F25DC773A252ABDACC1048D4E99B63705BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6341E1FE-0DD6-411C-974F-69D09C88A2F2}"/>
+  <xr:revisionPtr revIDLastSave="225" documentId="11_F25DC773A252ABDACC1048D4E99B63705BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0511EAEA-48DE-4656-BE10-35AB2ABFD474}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="testData" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="46">
   <si>
     <t>testCase_ID</t>
   </si>
@@ -162,7 +162,7 @@
     <t>B3;P2</t>
   </si>
   <si>
-    <t>TEST-1999</t>
+    <t>TEST-001</t>
   </si>
 </sst>
 </file>
@@ -487,21 +487,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="29.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="29.6640625" customWidth="1"/>
     <col min="9" max="9" width="24" bestFit="1" customWidth="1"/>
     <col min="10" max="15" width="24" customWidth="1"/>
-    <col min="16" max="21" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="21" width="5.6640625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="9" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="8.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -578,7 +578,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -610,7 +610,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -636,7 +636,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>38</v>
       </c>
@@ -665,9 +665,36 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>45</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P5" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>12</v>
+      </c>
+      <c r="R5" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" t="s">
+        <v>14</v>
+      </c>
+      <c r="V5" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
